--- a/_land_extras/toji-auction-imjang-note.xlsx
+++ b/_land_extras/toji-auction-imjang-note.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
+  <workbookProtection workbookPassword="EF6F" lockStructure="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
   </fonts>
   <fills count="6">
     <fill>
@@ -96,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -117,6 +118,12 @@
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +487,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AJ301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -22006,17 +22013,26 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0" password="EF6F"/>
   <autoFilter ref="A1:AJ301"/>
   <dataValidations count="2">
     <dataValidation sqref="E2:E301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"농지,농지외"</formula1>
     </dataValidation>
     <dataValidation sqref="X2:X301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"입찰,보류,패스"</formula1>
+      <formula1>"입찰,매입,보류,패스"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C토지 경매 임장 노트 · © Land Master Pro (land.free336.com)</oddHeader>
+    <oddFooter>&amp;C무단 수정·재배포 금지 · &amp;P/&amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -22026,7 +22042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -22039,13 +22055,11 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>사용법</t>
+          <t>1. 노란 칸에만 입력하세요. 초록 칸은 수식이라 잠겨 있습니다(시트 보호 적용, 필터·정렬은 사용 가능).</t>
         </is>
       </c>
     </row>
@@ -22077,9 +22091,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
@@ -22115,9 +22127,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -22125,7 +22135,43 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>저작권 · 이용 조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>© 2026 Land Master Pro (land.free336.com). 모든 권리 보유.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>개인의 학습·기록 목적 사용은 무료입니다. 저작권자의 허락 없이 ① 내용·구조·수식을 수정해 배포하는 것 ② 판매하거나 유료 자료에 포함하는 것 ③ 저작권 표시를 지우는 것 ④ 다른 사이트·카페·자료에 복제·게시하는 것을 금지합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>다른 분에게 알려 주실 때는 파일이 아니라 받는 곳 주소(https://land.free336.com/imjang-note.html)를 알려 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>시트 보호는 실수로 수식을 지우는 것을 막기 위한 장치이며, 저작권 보호의 대체 수단이 아닙니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="EF6F"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>